--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C836AD3-4024-4C49-A979-F4128650C74F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C14424A8-948F-4EC0-86C6-FF3444A62EE4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F0A0876-15E4-422F-ABEF-0D54A3DC13D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30659B71-02DB-487A-B919-9F930D913463}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63CA653E-7C69-407B-A383-24E33D63FA0D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0618CC07-942F-46DF-B02B-19BF4A089D51}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C14424A8-948F-4EC0-86C6-FF3444A62EE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E0FB537-75D0-4F84-91B8-075E5250F728}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30659B71-02DB-487A-B919-9F930D913463}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{783CDE81-5809-4C21-9E60-6865649CB024}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0618CC07-942F-46DF-B02B-19BF4A089D51}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{403C4211-5DB4-47E8-80BD-BD06B9D3B8B3}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7642,22 +7642,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C836AD3-4024-4C49-A979-F4128650C74F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65CC3943-D2EF-4F35-9F31-8985EF61E07E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F0A0876-15E4-422F-ABEF-0D54A3DC13D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DD4461D-5FCF-4722-B7B6-E19146D10912}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63CA653E-7C69-407B-A383-24E33D63FA0D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F68788B-3841-43A3-BDF3-DE3AA27DC9D8}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7642,22 +7642,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E0FB537-75D0-4F84-91B8-075E5250F728}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D1D7CD9-C02A-4F45-AD17-876AC4714944}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{783CDE81-5809-4C21-9E60-6865649CB024}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EEC0442-D377-4289-81F5-B680137C6BC7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{403C4211-5DB4-47E8-80BD-BD06B9D3B8B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1ED43B5C-DD0B-4D42-8FD8-40650AB154B7}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D1D7CD9-C02A-4F45-AD17-876AC4714944}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54634D5A-7DF5-48BB-A577-ECA5062DB6F7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EEC0442-D377-4289-81F5-B680137C6BC7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E00629A0-C850-4F06-9726-5591F1D5005D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1ED43B5C-DD0B-4D42-8FD8-40650AB154B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C093065-D998-4DDF-AB41-BA080A8A877C}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54634D5A-7DF5-48BB-A577-ECA5062DB6F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99B984EB-1E8E-4786-BE0F-48259C42FD8C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E00629A0-C850-4F06-9726-5591F1D5005D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48BB15E3-BF6C-4283-A839-8A4809067879}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C093065-D998-4DDF-AB41-BA080A8A877C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C3AE819-6E1D-4E40-9B16-851420B57481}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99B984EB-1E8E-4786-BE0F-48259C42FD8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{536CABDA-D4A6-42CB-9086-42BE5D10BEE0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48BB15E3-BF6C-4283-A839-8A4809067879}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7C24A17-022D-46BE-A9DE-C16277D386B6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C3AE819-6E1D-4E40-9B16-851420B57481}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8435BB4B-0117-46D2-B303-9E744B0AEB89}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{536CABDA-D4A6-42CB-9086-42BE5D10BEE0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2217283F-076B-44FE-95A3-AF0EEACB04FA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7C24A17-022D-46BE-A9DE-C16277D386B6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1F6AEF6-E2CA-4FA7-B052-4F24270CC3ED}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8435BB4B-0117-46D2-B303-9E744B0AEB89}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BFA958A-41F0-48B5-9104-A6397D1DF6E3}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2217283F-076B-44FE-95A3-AF0EEACB04FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01CA6C0C-1F40-4F71-9CBF-FC97373EFA79}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1F6AEF6-E2CA-4FA7-B052-4F24270CC3ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38177F9D-03DA-45B8-A9AB-AB7C3280EEF8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BFA958A-41F0-48B5-9104-A6397D1DF6E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5132B95B-92C9-4E31-BBBB-289215B4D963}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01CA6C0C-1F40-4F71-9CBF-FC97373EFA79}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBE21DAA-D718-4EE0-BDFF-8999280AAF10}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38177F9D-03DA-45B8-A9AB-AB7C3280EEF8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11A35A4D-149A-49C2-9C20-A0DF147021AC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5132B95B-92C9-4E31-BBBB-289215B4D963}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{772A104B-35D6-409A-99C0-8C46CD8AB843}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBE21DAA-D718-4EE0-BDFF-8999280AAF10}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0F8A6A0-655E-4FF1-9446-0CD28DD8471A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11A35A4D-149A-49C2-9C20-A0DF147021AC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{231CC67B-87C7-474F-9F48-D8FCEC255A7F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{772A104B-35D6-409A-99C0-8C46CD8AB843}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1AA5AED-3FA7-427D-B934-F2F24C95EDB7}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0F8A6A0-655E-4FF1-9446-0CD28DD8471A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3A0BC35-8550-4E4B-8828-FDBD70B99A65}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{231CC67B-87C7-474F-9F48-D8FCEC255A7F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0C7F873-CB7E-4EAD-822A-A668AE59B587}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1AA5AED-3FA7-427D-B934-F2F24C95EDB7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D01AF52-50C1-4B02-830F-CC76A21266F3}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3A0BC35-8550-4E4B-8828-FDBD70B99A65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD21A631-A3EA-4F9A-8085-116B3212BCB2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0C7F873-CB7E-4EAD-822A-A668AE59B587}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57638A27-E68A-4851-8156-6EE8B17D3ABD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D01AF52-50C1-4B02-830F-CC76A21266F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61066C20-99C0-4CAC-B858-7AA62CF7DD84}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD21A631-A3EA-4F9A-8085-116B3212BCB2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86B3C490-914F-46B6-B8C6-8148C7BEE4A4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57638A27-E68A-4851-8156-6EE8B17D3ABD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AAEC337-1651-407E-9366-2B369BA051B8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61066C20-99C0-4CAC-B858-7AA62CF7DD84}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A89AA8ED-BB94-43CA-B2A1-49EFDFC0BC76}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86B3C490-914F-46B6-B8C6-8148C7BEE4A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E25AE6C2-72B9-4EEE-97D9-51E18DE03125}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AAEC337-1651-407E-9366-2B369BA051B8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{203CB918-BB6B-4F6B-816E-5C5BA4E31139}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A89AA8ED-BB94-43CA-B2A1-49EFDFC0BC76}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{430C5DE7-C75A-40AC-8453-DA32382C9845}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E25AE6C2-72B9-4EEE-97D9-51E18DE03125}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF14FFB6-08BA-4F48-AC55-B8CAE0438F45}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{203CB918-BB6B-4F6B-816E-5C5BA4E31139}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7609151-5FC3-4C01-866D-085F496E6259}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{430C5DE7-C75A-40AC-8453-DA32382C9845}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B5B3847-FDC6-46DF-97EE-25167A7B73F1}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF14FFB6-08BA-4F48-AC55-B8CAE0438F45}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2265BC0F-56F7-4303-A89E-D9C8013828D3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7609151-5FC3-4C01-866D-085F496E6259}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BA904C7-D6F9-4A7A-898C-C158E846DC7F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B5B3847-FDC6-46DF-97EE-25167A7B73F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAF4F973-0A42-445E-95FC-0A797B13B07F}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2265BC0F-56F7-4303-A89E-D9C8013828D3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF174230-B958-4DE7-B83B-6E8E6A04E266}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BA904C7-D6F9-4A7A-898C-C158E846DC7F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDE719B8-D33D-42C3-8818-6FCC46F7819A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAF4F973-0A42-445E-95FC-0A797B13B07F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{521E7547-A185-41A0-A79B-64814FEB0634}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF174230-B958-4DE7-B83B-6E8E6A04E266}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B368FE93-89CA-4D14-B4C4-1C13ED4BB949}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDE719B8-D33D-42C3-8818-6FCC46F7819A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDBE0A71-B336-42CA-A4D3-17467BD007BB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{521E7547-A185-41A0-A79B-64814FEB0634}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D4145C1-243F-40F5-A878-035A0E4F64B3}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B368FE93-89CA-4D14-B4C4-1C13ED4BB949}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F2AA923-1DEB-40E2-AEE7-231680409C97}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDBE0A71-B336-42CA-A4D3-17467BD007BB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA53EFBF-A7D9-431E-A954-8F48C3BC79C5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D4145C1-243F-40F5-A878-035A0E4F64B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DD38FB0-28FE-494F-A3F7-5A1668C3F6D0}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F2AA923-1DEB-40E2-AEE7-231680409C97}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3A1F197-3B51-41DA-ADB3-9DFFC1065B7F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA53EFBF-A7D9-431E-A954-8F48C3BC79C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9843D389-6F31-4671-B170-4A4BFB4FCBA0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DD38FB0-28FE-494F-A3F7-5A1668C3F6D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F93E798-84D9-4238-AD38-B48576DF37AD}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3A1F197-3B51-41DA-ADB3-9DFFC1065B7F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{575070B4-BEDA-4C29-BAB9-9E02C0DB676B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9843D389-6F31-4671-B170-4A4BFB4FCBA0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41765398-0441-4C84-BD2C-172839D31D06}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F93E798-84D9-4238-AD38-B48576DF37AD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B8DF144-8DBE-4B9A-AAEB-3C632ABD9C14}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_baker.xlsx
+++ b/____EvoM1_TraitTable/dexterity_baker.xlsx
@@ -7651,13 +7651,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{575070B4-BEDA-4C29-BAB9-9E02C0DB676B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{487C4FAF-3228-4C16-B090-AFDA87645052}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41765398-0441-4C84-BD2C-172839D31D06}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7DC0AC2-E288-48E7-8362-BCEECD76F436}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B8DF144-8DBE-4B9A-AAEB-3C632ABD9C14}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E9B2163-F710-434E-BA80-671360B7CADB}"/>
 </file>